--- a/Clash_of_Cards.xlsx
+++ b/Clash_of_Cards.xlsx
@@ -3692,7 +3692,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Super Minion</t>
+          <t>Inferno Dragon</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -3700,14 +3700,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F53" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_52_super_minion.png</t>
+          <t>coc/cards/super_troop_52_inferno_dragon.png</t>
         </is>
       </c>
     </row>

--- a/Clash_of_Cards.xlsx
+++ b/Clash_of_Cards.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,7 +47,7 @@
     </font>
     <font>
       <color rgb="00666666"/>
-      <sz val="9"/>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -59,9 +59,6 @@
     <font>
       <b val="1"/>
       <color rgb="000033AA"/>
-    </font>
-    <font>
-      <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
@@ -136,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -176,10 +173,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -265,7 +259,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -290,7 +284,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -315,7 +309,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -340,7 +334,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -365,7 +359,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -390,7 +384,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -415,7 +409,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -440,7 +434,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -465,7 +459,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -490,7 +484,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -515,7 +509,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -540,7 +534,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -565,7 +559,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -590,7 +584,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -615,7 +609,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -640,7 +634,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -665,7 +659,7 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -690,7 +684,7 @@
       <row>18</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -715,7 +709,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="19" name="Image 19" descr="Picture"/>
@@ -740,7 +734,7 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -765,7 +759,7 @@
       <row>21</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="21" name="Image 21" descr="Picture"/>
@@ -790,7 +784,7 @@
       <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -815,7 +809,7 @@
       <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="23" name="Image 23" descr="Picture"/>
@@ -840,7 +834,7 @@
       <row>24</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -865,7 +859,7 @@
       <row>25</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -890,7 +884,7 @@
       <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -915,7 +909,7 @@
       <row>27</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="27" name="Image 27" descr="Picture"/>
@@ -940,7 +934,7 @@
       <row>28</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -965,7 +959,7 @@
       <row>29</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -990,7 +984,7 @@
       <row>30</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="30" name="Image 30" descr="Picture"/>
@@ -1015,7 +1009,7 @@
       <row>31</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="31" name="Image 31" descr="Picture"/>
@@ -1040,7 +1034,7 @@
       <row>32</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="32" name="Image 32" descr="Picture"/>
@@ -1065,7 +1059,7 @@
       <row>33</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="33" name="Image 33" descr="Picture"/>
@@ -1090,7 +1084,7 @@
       <row>34</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="34" name="Image 34" descr="Picture"/>
@@ -1115,7 +1109,7 @@
       <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="35" name="Image 35" descr="Picture"/>
@@ -1140,7 +1134,7 @@
       <row>36</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>
@@ -1165,7 +1159,7 @@
       <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="37" name="Image 37" descr="Picture"/>
@@ -1190,7 +1184,7 @@
       <row>38</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="38" name="Image 38" descr="Picture"/>
@@ -1215,7 +1209,7 @@
       <row>39</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="39" name="Image 39" descr="Picture"/>
@@ -1240,7 +1234,7 @@
       <row>40</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="40" name="Image 40" descr="Picture"/>
@@ -1265,7 +1259,7 @@
       <row>41</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="41" name="Image 41" descr="Picture"/>
@@ -1290,7 +1284,7 @@
       <row>42</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="42" name="Image 42" descr="Picture"/>
@@ -1315,7 +1309,7 @@
       <row>43</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="43" name="Image 43" descr="Picture"/>
@@ -1340,7 +1334,7 @@
       <row>44</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="44" name="Image 44" descr="Picture"/>
@@ -1365,7 +1359,7 @@
       <row>45</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="45" name="Image 45" descr="Picture"/>
@@ -1390,7 +1384,7 @@
       <row>46</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="46" name="Image 46" descr="Picture"/>
@@ -1415,7 +1409,7 @@
       <row>47</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="47" name="Image 47" descr="Picture"/>
@@ -1440,7 +1434,7 @@
       <row>48</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="48" name="Image 48" descr="Picture"/>
@@ -1465,7 +1459,7 @@
       <row>49</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="49" name="Image 49" descr="Picture"/>
@@ -1490,7 +1484,7 @@
       <row>50</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="50" name="Image 50" descr="Picture"/>
@@ -1515,7 +1509,7 @@
       <row>51</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="51" name="Image 51" descr="Picture"/>
@@ -1540,7 +1534,7 @@
       <row>52</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="52" name="Image 52" descr="Picture"/>
@@ -1565,7 +1559,7 @@
       <row>53</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="53" name="Image 53" descr="Picture"/>
@@ -1590,7 +1584,7 @@
       <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="54" name="Image 54" descr="Picture"/>
@@ -1615,7 +1609,7 @@
       <row>55</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="55" name="Image 55" descr="Picture"/>
@@ -1640,7 +1634,7 @@
       <row>56</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="56" name="Image 56" descr="Picture"/>
@@ -1665,7 +1659,7 @@
       <row>57</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="57" name="Image 57" descr="Picture"/>
@@ -1690,7 +1684,7 @@
       <row>58</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="58" name="Image 58" descr="Picture"/>
@@ -1715,7 +1709,7 @@
       <row>59</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="59" name="Image 59" descr="Picture"/>
@@ -1740,7 +1734,7 @@
       <row>60</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="419100" cy="419100"/>
+    <ext cx="381000" cy="381000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="60" name="Image 60" descr="Picture"/>
@@ -2053,13 +2047,13 @@
   <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2095,11 +2089,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Icon File</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="46" customHeight="1">
+          <t>Image (app path)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -2126,11 +2120,11 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_01_barbarian.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/barbarian.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -2157,11 +2151,11 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_02_archer.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/archer.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -2188,11 +2182,11 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_03_giant.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/giant.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -2219,11 +2213,11 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_04_goblin.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/goblin.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -2250,11 +2244,11 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_05_wall_breaker.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/wall-breaker.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -2281,11 +2275,11 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_06_balloon.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/balloon.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -2312,11 +2306,11 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_07_wizard.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/wizard.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -2343,11 +2337,11 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_08_healer.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/healer.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -2374,11 +2368,11 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_09_dragon.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/dragon.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -2405,11 +2399,11 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_10_pekka.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/p-e-k-k-a.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -2436,11 +2430,11 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_11_baby_dragon.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/baby-dragon.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -2467,11 +2461,11 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_12_miner.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/miner.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -2498,11 +2492,11 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_13_electro_dragon.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/electro-dragon.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -2529,11 +2523,11 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_14_yeti.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/yeti.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -2560,11 +2554,11 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_15_dragon_rider.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/dragon-rider.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -2591,11 +2585,11 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_16_electro_titan.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/electro-titan.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -2622,11 +2616,11 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_17_root_rider.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/root-rider.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -2653,11 +2647,11 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_18_thrower.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/thrower.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -2684,11 +2678,11 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/elixir_19_meteor_golem.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/meteor-golem.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -2715,11 +2709,11 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_20_minion.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/minion.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -2746,11 +2740,11 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_21_hog_rider.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/hog-rider.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -2777,11 +2771,11 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_22_valkyrie.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/valkyrie.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -2808,11 +2802,11 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_23_golem.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/golem.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -2839,11 +2833,11 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_24_witch.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/witch.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -2870,11 +2864,11 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_25_lava_hound.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/lava-hound.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -2901,11 +2895,11 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_26_bowler.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/bowler.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
@@ -2932,11 +2926,11 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_27_ice_golem.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/ice-golem.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
@@ -2963,11 +2957,11 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_28_headhunter.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/headhunter.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
@@ -2994,11 +2988,11 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_29_apprentice_warden.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/apprentice-warden.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
@@ -3025,11 +3019,11 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_30_druid.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/druid.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -3056,11 +3050,11 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_31_furnace.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/furnace.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
@@ -3087,11 +3081,11 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/dark_elixir_32_ruin_witch.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/ruin-witch.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -3118,11 +3112,11 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/builder_base_33_raged_barbarian.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/raged-barbarian.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
@@ -3149,11 +3143,11 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/builder_base_34_sneaky_archer.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/sneaky-archer.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
@@ -3180,11 +3174,11 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/builder_base_35_boxer_giant.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/boxer-giant.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
@@ -3211,11 +3205,11 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/builder_base_36_beta_minion.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/beta-minion.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
@@ -3242,11 +3236,11 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/builder_base_37_bomber.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/bomber.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
@@ -3273,11 +3267,11 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/builder_base_38_baby_dragon_builder.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/baby-dragon.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
@@ -3304,11 +3298,11 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/builder_base_39_cannon_cart.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/cannon-cart.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
@@ -3335,11 +3329,11 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/builder_base_40_night_witch.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/night-witch.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
@@ -3366,11 +3360,11 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/builder_base_41_drop_ship.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/drop-ship.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
@@ -3397,11 +3391,11 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/builder_base_42_power_pekka.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/power-p-e-k-k-a.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
@@ -3428,11 +3422,11 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/builder_base_43_hog_glider.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/hog-glider.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
@@ -3459,11 +3453,11 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_44_super_barbarian.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/super-barbarian.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
@@ -3490,11 +3484,11 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_45_super_archer.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/super-archer.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
@@ -3521,11 +3515,11 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_46_super_giant.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/super-giant.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
@@ -3552,11 +3546,11 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_47_sneaky_goblin.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/sneaky-goblin.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
@@ -3583,11 +3577,11 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_48_super_wall_breaker.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/super-wall-breaker.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
@@ -3614,11 +3608,11 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_49_rocket_balloon.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/rocket-balloon.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
@@ -3645,11 +3639,11 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_50_super_wizard.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/super-wizard.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
@@ -3661,7 +3655,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Inferno Dragon</t>
+          <t>Super Dragon</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -3669,18 +3663,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F52" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_51_inferno_dragon.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/super-dragon.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
@@ -3707,11 +3701,11 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_52_inferno_dragon.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/inferno-dragon.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
@@ -3731,18 +3725,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F54" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_53_super_miner.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/super-miner.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
@@ -3769,11 +3763,11 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_54_super_yeti.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/super-yeti.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
@@ -3800,11 +3794,11 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_55_super_minion.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/super-minion.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
@@ -3824,18 +3818,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F57" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_56_super_hog_rider.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/super-hog-rider.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
@@ -3847,7 +3841,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Super Dragon</t>
+          <t>Super Valkyrie</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -3855,18 +3849,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F58" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_57_super_dragon.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/super-valkyrie.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
@@ -3886,18 +3880,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="F59" s="15" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="F59" s="11" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_58_super_witch.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/super-witch.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
@@ -3924,11 +3918,11 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_59_ice_hound.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="46" customHeight="1">
+          <t>/coc/wiki/troops/ice-hound.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
@@ -3955,7 +3949,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>coc/cards/super_troop_60_super_bowler.png</t>
+          <t>/coc/wiki/troops/super-bowler.webp</t>
         </is>
       </c>
     </row>
@@ -3972,7 +3966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3982,22 +3976,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Collected</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Remaining</t>
         </is>
@@ -4081,6 +4075,30 @@
       </c>
       <c r="D6" t="n">
         <v>47</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>One image per card, from web/public/coc/wiki/troops (Supercell, Fan Content Policy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Greyscale</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Un-held cards render the same image under CSS grayscale(1) — no separate bw file.</t>
+        </is>
       </c>
     </row>
   </sheetData>
